--- a/outputs/38823.xlsx
+++ b/outputs/38823.xlsx
@@ -161,39 +161,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -457,7 +457,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
@@ -466,7 +466,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -477,7 +477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>44562</v>
       </c>
@@ -494,7 +494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>44563</v>
       </c>
@@ -518,7 +518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>44564</v>
       </c>
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>44565</v>
       </c>
@@ -554,7 +554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>44566</v>
       </c>
@@ -572,7 +572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>44567</v>
       </c>
@@ -583,7 +583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>44568</v>
       </c>
@@ -594,7 +594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>44569</v>
       </c>
@@ -605,7 +605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>44570</v>
       </c>
@@ -616,7 +616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>44571</v>
       </c>
@@ -627,7 +627,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>44572</v>
       </c>
@@ -638,7 +638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>44573</v>
       </c>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>44574</v>
       </c>

--- a/outputs/38823.xlsx
+++ b/outputs/38823.xlsx
@@ -514,7 +514,7 @@
         <v>7</v>
       </c>
       <c r="I4" s="2" t="n">
-        <f aca="false">SUMIFS($C$3:$C$15,$A$3:$A$15,"&gt;="&amp;$E$4,$A$3:$A$15,"&lt;="&amp;$F$4,$B$3:$B$15,"*"&amp;H4&amp;"*")</f>
+        <f aca="false">SUMPRODUCT((A$3:A$15&gt;=E4)*(A$3:A$15&lt;=F4)*(ISNUMBER(SEARCH(H4,B$3:B$15)))*C$3:C$15)</f>
         <v>22</v>
       </c>
     </row>
@@ -532,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="2" t="n">
-        <f aca="false">SUMIFS($C$3:$C$15,$A$3:$A$15,"&gt;="&amp;$E$4,$A$3:$A$15,"&lt;="&amp;$F$4,$B$3:$B$15,"*"&amp;H5&amp;"*")</f>
+        <f aca="false">SUMPRODUCT((A$3:A$15&gt;=E4)*(A$3:A$15&lt;=F4)*(ISNUMBER(SEARCH(H5,B$3:B$15)))*C$3:C$15)</f>
         <v>12</v>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="2" t="n">
-        <f aca="false">SUMIFS($C$3:$C$15,$A$3:$A$15,"&gt;="&amp;$E$4,$A$3:$A$15,"&lt;="&amp;$F$4,$B$3:$B$15,"*"&amp;H6&amp;"*")</f>
+        <f aca="false">SUMPRODUCT((A$3:A$15&gt;=E4)*(A$3:A$15&lt;=F4)*(ISNUMBER(SEARCH(H6,B$3:B$15)))*C$3:C$15)</f>
         <v>9</v>
       </c>
     </row>
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="2" t="n">
-        <f aca="false">SUMIFS($C$3:$C$15,$A$3:$A$15,"&gt;="&amp;$E$4,$A$3:$A$15,"&lt;="&amp;$F$4,$B$3:$B$15,"*"&amp;H7&amp;"*")</f>
+        <f aca="false">SUMPRODUCT((A$3:A$15&gt;=E4)*(A$3:A$15&lt;=F4)*(ISNUMBER(SEARCH(H7,B$3:B$15)))*C$3:C$15)</f>
         <v>4</v>
       </c>
     </row>
